--- a/Datos limpios/Pricing diario/Histórico/Sorgo.xlsx
+++ b/Datos limpios/Pricing diario/Histórico/Sorgo.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2864"/>
+  <dimension ref="A1:K2869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -106349,301 +106349,192 @@
         </is>
       </c>
     </row>
+    <row r="2865">
+      <c r="A2865" s="2">
+        <v>45950</v>
+      </c>
+      <c r="B2865">
+        <v>619.9299999999999</v>
+      </c>
+      <c r="C2865">
+        <v>11.96</v>
+      </c>
+      <c r="D2865">
+        <v>0</v>
+      </c>
+      <c r="E2865">
+        <v>631.89</v>
+      </c>
+      <c r="F2865">
+        <v>0</v>
+      </c>
+      <c r="G2865">
+        <v>0</v>
+      </c>
+      <c r="H2865">
+        <v>0</v>
+      </c>
+      <c r="I2865">
+        <v>0</v>
+      </c>
+      <c r="J2865">
+        <v>631.89</v>
+      </c>
+      <c r="K2865" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B2866">
+        <v>732.8200000000001</v>
+      </c>
+      <c r="C2866">
+        <v>0</v>
+      </c>
+      <c r="D2866">
+        <v>33.98</v>
+      </c>
+      <c r="E2866">
+        <v>698.84</v>
+      </c>
+      <c r="F2866">
+        <v>390</v>
+      </c>
+      <c r="G2866">
+        <v>0</v>
+      </c>
+      <c r="H2866">
+        <v>0</v>
+      </c>
+      <c r="I2866">
+        <v>390</v>
+      </c>
+      <c r="J2866">
+        <v>1088.84</v>
+      </c>
+      <c r="K2866" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" s="2">
+        <v>45952</v>
+      </c>
+      <c r="B2867">
+        <v>1191.28</v>
+      </c>
+      <c r="C2867">
+        <v>22.39</v>
+      </c>
+      <c r="D2867">
+        <v>0</v>
+      </c>
+      <c r="E2867">
+        <v>1213.67</v>
+      </c>
+      <c r="F2867">
+        <v>454</v>
+      </c>
+      <c r="G2867">
+        <v>0</v>
+      </c>
+      <c r="H2867">
+        <v>0</v>
+      </c>
+      <c r="I2867">
+        <v>454</v>
+      </c>
+      <c r="J2867">
+        <v>1667.67</v>
+      </c>
+      <c r="K2867" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" s="2">
+        <v>45953</v>
+      </c>
+      <c r="B2868">
+        <v>3461.9</v>
+      </c>
+      <c r="C2868">
+        <v>0</v>
+      </c>
+      <c r="D2868">
+        <v>0</v>
+      </c>
+      <c r="E2868">
+        <v>3461.9</v>
+      </c>
+      <c r="F2868">
+        <v>230</v>
+      </c>
+      <c r="G2868">
+        <v>0</v>
+      </c>
+      <c r="H2868">
+        <v>0</v>
+      </c>
+      <c r="I2868">
+        <v>230</v>
+      </c>
+      <c r="J2868">
+        <v>3691.9</v>
+      </c>
+      <c r="K2868" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B2869">
+        <v>424.49</v>
+      </c>
+      <c r="C2869">
+        <v>0</v>
+      </c>
+      <c r="D2869">
+        <v>0</v>
+      </c>
+      <c r="E2869">
+        <v>424.49</v>
+      </c>
+      <c r="F2869">
+        <v>260</v>
+      </c>
+      <c r="G2869">
+        <v>0</v>
+      </c>
+      <c r="H2869">
+        <v>0</v>
+      </c>
+      <c r="I2869">
+        <v>260</v>
+      </c>
+      <c r="J2869">
+        <v>684.49</v>
+      </c>
+      <c r="K2869" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bac5de4a034fee97af64ba5a2822cd53">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="027d3429df443898fbbc0b888682b5bf" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E634C15-DB4D-4BD5-8EDF-C32E7CF82806}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD636667-07A6-40EC-BAFD-D6238586C3DE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55B53F68-C590-4410-863A-8CD4050835A4}"/>
 </file>
--- a/Datos limpios/Pricing diario/Histórico/Sorgo.xlsx
+++ b/Datos limpios/Pricing diario/Histórico/Sorgo.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2869"/>
+  <dimension ref="A1:K2889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -106317,16 +106317,16 @@
         <v>45947</v>
       </c>
       <c r="B2864">
-        <v>18404.82</v>
+        <v>17904.82</v>
       </c>
       <c r="C2864">
         <v>0</v>
       </c>
       <c r="D2864">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E2864">
-        <v>18404.82</v>
+        <v>17404.82</v>
       </c>
       <c r="F2864">
         <v>60.13</v>
@@ -106341,7 +106341,7 @@
         <v>60.13</v>
       </c>
       <c r="J2864">
-        <v>18464.95</v>
+        <v>17464.95</v>
       </c>
       <c r="K2864" t="inlineStr">
         <is>
@@ -106529,6 +106529,746 @@
         <v>684.49</v>
       </c>
       <c r="K2869" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" s="2">
+        <v>45957</v>
+      </c>
+      <c r="B2870">
+        <v>775</v>
+      </c>
+      <c r="C2870">
+        <v>0</v>
+      </c>
+      <c r="D2870">
+        <v>0</v>
+      </c>
+      <c r="E2870">
+        <v>775</v>
+      </c>
+      <c r="F2870">
+        <v>514.08</v>
+      </c>
+      <c r="G2870">
+        <v>0</v>
+      </c>
+      <c r="H2870">
+        <v>0</v>
+      </c>
+      <c r="I2870">
+        <v>514.08</v>
+      </c>
+      <c r="J2870">
+        <v>1289.08</v>
+      </c>
+      <c r="K2870" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B2871">
+        <v>1520.12</v>
+      </c>
+      <c r="C2871">
+        <v>0</v>
+      </c>
+      <c r="D2871">
+        <v>0</v>
+      </c>
+      <c r="E2871">
+        <v>1520.12</v>
+      </c>
+      <c r="F2871">
+        <v>36</v>
+      </c>
+      <c r="G2871">
+        <v>0</v>
+      </c>
+      <c r="H2871">
+        <v>0</v>
+      </c>
+      <c r="I2871">
+        <v>36</v>
+      </c>
+      <c r="J2871">
+        <v>1556.12</v>
+      </c>
+      <c r="K2871" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B2872">
+        <v>164.4</v>
+      </c>
+      <c r="C2872">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="D2872">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="E2872">
+        <v>164.4</v>
+      </c>
+      <c r="F2872">
+        <v>1500</v>
+      </c>
+      <c r="G2872">
+        <v>0</v>
+      </c>
+      <c r="H2872">
+        <v>0</v>
+      </c>
+      <c r="I2872">
+        <v>1500</v>
+      </c>
+      <c r="J2872">
+        <v>1664.4</v>
+      </c>
+      <c r="K2872" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B2873">
+        <v>561.78</v>
+      </c>
+      <c r="C2873">
+        <v>0</v>
+      </c>
+      <c r="D2873">
+        <v>0</v>
+      </c>
+      <c r="E2873">
+        <v>561.78</v>
+      </c>
+      <c r="F2873">
+        <v>330.28</v>
+      </c>
+      <c r="G2873">
+        <v>0</v>
+      </c>
+      <c r="H2873">
+        <v>0</v>
+      </c>
+      <c r="I2873">
+        <v>330.28</v>
+      </c>
+      <c r="J2873">
+        <v>892.0599999999999</v>
+      </c>
+      <c r="K2873" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B2874">
+        <v>1686.36</v>
+      </c>
+      <c r="C2874">
+        <v>59.08</v>
+      </c>
+      <c r="D2874">
+        <v>0</v>
+      </c>
+      <c r="E2874">
+        <v>1745.44</v>
+      </c>
+      <c r="F2874">
+        <v>6214.9</v>
+      </c>
+      <c r="G2874">
+        <v>0</v>
+      </c>
+      <c r="H2874">
+        <v>300</v>
+      </c>
+      <c r="I2874">
+        <v>5914.9</v>
+      </c>
+      <c r="J2874">
+        <v>7660.339999999999</v>
+      </c>
+      <c r="K2874" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B2875">
+        <v>579.28</v>
+      </c>
+      <c r="C2875">
+        <v>0</v>
+      </c>
+      <c r="D2875">
+        <v>0</v>
+      </c>
+      <c r="E2875">
+        <v>579.28</v>
+      </c>
+      <c r="F2875">
+        <v>2120</v>
+      </c>
+      <c r="G2875">
+        <v>0</v>
+      </c>
+      <c r="H2875">
+        <v>0</v>
+      </c>
+      <c r="I2875">
+        <v>2120</v>
+      </c>
+      <c r="J2875">
+        <v>2699.28</v>
+      </c>
+      <c r="K2875" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B2876">
+        <v>895.99</v>
+      </c>
+      <c r="C2876">
+        <v>0</v>
+      </c>
+      <c r="D2876">
+        <v>0</v>
+      </c>
+      <c r="E2876">
+        <v>895.99</v>
+      </c>
+      <c r="F2876">
+        <v>814.16</v>
+      </c>
+      <c r="G2876">
+        <v>0</v>
+      </c>
+      <c r="H2876">
+        <v>0</v>
+      </c>
+      <c r="I2876">
+        <v>814.16</v>
+      </c>
+      <c r="J2876">
+        <v>1710.15</v>
+      </c>
+      <c r="K2876" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B2877">
+        <v>1036.88</v>
+      </c>
+      <c r="C2877">
+        <v>500</v>
+      </c>
+      <c r="D2877">
+        <v>30</v>
+      </c>
+      <c r="E2877">
+        <v>1506.88</v>
+      </c>
+      <c r="F2877">
+        <v>3121.38</v>
+      </c>
+      <c r="G2877">
+        <v>0</v>
+      </c>
+      <c r="H2877">
+        <v>0</v>
+      </c>
+      <c r="I2877">
+        <v>3121.38</v>
+      </c>
+      <c r="J2877">
+        <v>4628.26</v>
+      </c>
+      <c r="K2877" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B2878">
+        <v>804.12</v>
+      </c>
+      <c r="C2878">
+        <v>11.44</v>
+      </c>
+      <c r="D2878">
+        <v>0</v>
+      </c>
+      <c r="E2878">
+        <v>815.5600000000001</v>
+      </c>
+      <c r="F2878">
+        <v>1130.72</v>
+      </c>
+      <c r="G2878">
+        <v>0</v>
+      </c>
+      <c r="H2878">
+        <v>0</v>
+      </c>
+      <c r="I2878">
+        <v>1130.72</v>
+      </c>
+      <c r="J2878">
+        <v>1946.28</v>
+      </c>
+      <c r="K2878" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B2879">
+        <v>1359.89</v>
+      </c>
+      <c r="C2879">
+        <v>0</v>
+      </c>
+      <c r="D2879">
+        <v>0</v>
+      </c>
+      <c r="E2879">
+        <v>1359.89</v>
+      </c>
+      <c r="F2879">
+        <v>849.1900000000001</v>
+      </c>
+      <c r="G2879">
+        <v>0</v>
+      </c>
+      <c r="H2879">
+        <v>0</v>
+      </c>
+      <c r="I2879">
+        <v>849.1900000000001</v>
+      </c>
+      <c r="J2879">
+        <v>2209.08</v>
+      </c>
+      <c r="K2879" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B2880">
+        <v>1321.14</v>
+      </c>
+      <c r="C2880">
+        <v>0</v>
+      </c>
+      <c r="D2880">
+        <v>0</v>
+      </c>
+      <c r="E2880">
+        <v>1321.14</v>
+      </c>
+      <c r="F2880">
+        <v>700</v>
+      </c>
+      <c r="G2880">
+        <v>0</v>
+      </c>
+      <c r="H2880">
+        <v>0</v>
+      </c>
+      <c r="I2880">
+        <v>700</v>
+      </c>
+      <c r="J2880">
+        <v>2021.14</v>
+      </c>
+      <c r="K2880" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B2881">
+        <v>797.55</v>
+      </c>
+      <c r="C2881">
+        <v>0</v>
+      </c>
+      <c r="D2881">
+        <v>0</v>
+      </c>
+      <c r="E2881">
+        <v>797.55</v>
+      </c>
+      <c r="F2881">
+        <v>640</v>
+      </c>
+      <c r="G2881">
+        <v>0</v>
+      </c>
+      <c r="H2881">
+        <v>0</v>
+      </c>
+      <c r="I2881">
+        <v>640</v>
+      </c>
+      <c r="J2881">
+        <v>1437.55</v>
+      </c>
+      <c r="K2881" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B2882">
+        <v>641.79</v>
+      </c>
+      <c r="C2882">
+        <v>106.67</v>
+      </c>
+      <c r="D2882">
+        <v>0</v>
+      </c>
+      <c r="E2882">
+        <v>748.4599999999999</v>
+      </c>
+      <c r="F2882">
+        <v>330</v>
+      </c>
+      <c r="G2882">
+        <v>0</v>
+      </c>
+      <c r="H2882">
+        <v>0</v>
+      </c>
+      <c r="I2882">
+        <v>330</v>
+      </c>
+      <c r="J2882">
+        <v>1078.46</v>
+      </c>
+      <c r="K2882" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B2883">
+        <v>1177.18</v>
+      </c>
+      <c r="C2883">
+        <v>0</v>
+      </c>
+      <c r="D2883">
+        <v>0</v>
+      </c>
+      <c r="E2883">
+        <v>1177.18</v>
+      </c>
+      <c r="F2883">
+        <v>704.3</v>
+      </c>
+      <c r="G2883">
+        <v>0</v>
+      </c>
+      <c r="H2883">
+        <v>0</v>
+      </c>
+      <c r="I2883">
+        <v>704.3</v>
+      </c>
+      <c r="J2883">
+        <v>1881.48</v>
+      </c>
+      <c r="K2883" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B2884">
+        <v>847.15</v>
+      </c>
+      <c r="C2884">
+        <v>0</v>
+      </c>
+      <c r="D2884">
+        <v>0</v>
+      </c>
+      <c r="E2884">
+        <v>847.15</v>
+      </c>
+      <c r="F2884">
+        <v>330</v>
+      </c>
+      <c r="G2884">
+        <v>0</v>
+      </c>
+      <c r="H2884">
+        <v>0</v>
+      </c>
+      <c r="I2884">
+        <v>330</v>
+      </c>
+      <c r="J2884">
+        <v>1177.15</v>
+      </c>
+      <c r="K2884" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B2885">
+        <v>145</v>
+      </c>
+      <c r="C2885">
+        <v>0</v>
+      </c>
+      <c r="D2885">
+        <v>0</v>
+      </c>
+      <c r="E2885">
+        <v>145</v>
+      </c>
+      <c r="F2885">
+        <v>0</v>
+      </c>
+      <c r="G2885">
+        <v>0</v>
+      </c>
+      <c r="H2885">
+        <v>0</v>
+      </c>
+      <c r="I2885">
+        <v>0</v>
+      </c>
+      <c r="J2885">
+        <v>145</v>
+      </c>
+      <c r="K2885" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B2886">
+        <v>473.95</v>
+      </c>
+      <c r="C2886">
+        <v>0</v>
+      </c>
+      <c r="D2886">
+        <v>0</v>
+      </c>
+      <c r="E2886">
+        <v>473.95</v>
+      </c>
+      <c r="F2886">
+        <v>270</v>
+      </c>
+      <c r="G2886">
+        <v>0</v>
+      </c>
+      <c r="H2886">
+        <v>0</v>
+      </c>
+      <c r="I2886">
+        <v>270</v>
+      </c>
+      <c r="J2886">
+        <v>743.95</v>
+      </c>
+      <c r="K2886" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B2887">
+        <v>420</v>
+      </c>
+      <c r="C2887">
+        <v>0</v>
+      </c>
+      <c r="D2887">
+        <v>0</v>
+      </c>
+      <c r="E2887">
+        <v>420</v>
+      </c>
+      <c r="F2887">
+        <v>60</v>
+      </c>
+      <c r="G2887">
+        <v>0</v>
+      </c>
+      <c r="H2887">
+        <v>0</v>
+      </c>
+      <c r="I2887">
+        <v>60</v>
+      </c>
+      <c r="J2887">
+        <v>480</v>
+      </c>
+      <c r="K2887" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B2888">
+        <v>332.46</v>
+      </c>
+      <c r="C2888">
+        <v>0</v>
+      </c>
+      <c r="D2888">
+        <v>0</v>
+      </c>
+      <c r="E2888">
+        <v>332.46</v>
+      </c>
+      <c r="F2888">
+        <v>130</v>
+      </c>
+      <c r="G2888">
+        <v>0</v>
+      </c>
+      <c r="H2888">
+        <v>0</v>
+      </c>
+      <c r="I2888">
+        <v>130</v>
+      </c>
+      <c r="J2888">
+        <v>462.46</v>
+      </c>
+      <c r="K2888" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B2889">
+        <v>1364.39</v>
+      </c>
+      <c r="C2889">
+        <v>120</v>
+      </c>
+      <c r="D2889">
+        <v>0</v>
+      </c>
+      <c r="E2889">
+        <v>1484.39</v>
+      </c>
+      <c r="F2889">
+        <v>543.34</v>
+      </c>
+      <c r="G2889">
+        <v>0</v>
+      </c>
+      <c r="H2889">
+        <v>0</v>
+      </c>
+      <c r="I2889">
+        <v>543.34</v>
+      </c>
+      <c r="J2889">
+        <v>2027.73</v>
+      </c>
+      <c r="K2889" t="inlineStr">
         <is>
           <t>SORGO</t>
         </is>
